--- a/pipeline.xlsx
+++ b/pipeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://angarbank.sharepoint.com/sites/GymCred/Documentos Compartilhados/Controle/Novos Negócios/Pipeline Academias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="6_{B1A76B9C-D489-8E4F-91C7-035E9F344680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A1FB3B5-CE7B-4D09-BDB3-D908C7CB0DD3}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="6_{B1A76B9C-D489-8E4F-91C7-035E9F344680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72CAD181-1DF2-4661-A330-8A086D84B0B9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8017BD0A-1660-4F0C-B9A9-E8E9DC9F561E}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t>Supertech</t>
   </si>
   <si>
-    <t>Desembolso</t>
-  </si>
-  <si>
     <t>Metal Fitness</t>
   </si>
   <si>
@@ -378,7 +375,10 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>Segundo semestre</t>
+    <t>Desembolsado</t>
+  </si>
+  <si>
+    <t>2S2026</t>
   </si>
 </sst>
 </file>
@@ -440,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -465,7 +465,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -848,18 +847,18 @@
         <v>13</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
@@ -889,22 +888,22 @@
         <f t="shared" ref="J2" si="2">F2/(1-G2)</f>
         <v>1128949.9468085107</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="8">
         <v>46142</v>
       </c>
       <c r="L2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>125004</v>
@@ -931,16 +930,16 @@
         <f t="shared" ref="J3" si="3">F3/(1-G3)</f>
         <v>107530.32258064518</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="8">
         <v>46142</v>
       </c>
       <c r="L3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -973,11 +972,11 @@
         <f t="shared" ref="J4:J8" si="4">F4/(1-G4)</f>
         <v>2010749.0566844919</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="8">
         <v>46142</v>
       </c>
       <c r="L4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -1015,11 +1014,11 @@
         <f t="shared" si="4"/>
         <v>396984.34285714291</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="8">
         <v>46099</v>
       </c>
       <c r="L5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -1057,12 +1056,12 @@
         <f t="shared" si="4"/>
         <v>192304.76190476192</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="8">
         <f>K4+1</f>
         <v>46143</v>
       </c>
       <c r="L6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -1100,17 +1099,17 @@
         <f t="shared" si="4"/>
         <v>660094.05882352928</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="8">
         <f>K6+1</f>
         <v>46144</v>
       </c>
       <c r="L7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -1143,12 +1142,12 @@
         <f t="shared" si="4"/>
         <v>966773.04812834226</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="8">
         <f>K7+1</f>
         <v>46145</v>
       </c>
       <c r="L8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -1187,11 +1186,11 @@
         <f>F9/(1-G9)</f>
         <v>665116.96256684489</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="8">
         <v>46099</v>
       </c>
       <c r="L9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M9" s="1"/>
     </row>
@@ -1203,7 +1202,7 @@
         <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D10" s="3">
         <f>F10/(1-E10)</f>
@@ -1230,23 +1229,23 @@
         <f>F10/(1-G10)</f>
         <v>583672.3675675675</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D11" s="3">
         <f>F11/(1-E11)</f>
@@ -1273,11 +1272,11 @@
         <f>F11/(1-G11)</f>
         <v>322580.64516129036</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M11" s="1"/>
     </row>
@@ -1316,11 +1315,11 @@
         <f t="shared" ref="J12:J23" si="9">F12+I12</f>
         <v>1680000</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -1358,11 +1357,11 @@
         <f t="shared" si="9"/>
         <v>1680000</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1400,11 +1399,11 @@
         <f t="shared" si="9"/>
         <v>1680000</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -1442,11 +1441,11 @@
         <f t="shared" si="9"/>
         <v>3360000</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -1484,11 +1483,11 @@
         <f t="shared" si="9"/>
         <v>1680000</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -1526,11 +1525,11 @@
         <f t="shared" si="9"/>
         <v>2940000</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -1568,11 +1567,11 @@
         <f t="shared" si="9"/>
         <v>2822400</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -1610,11 +1609,11 @@
         <f t="shared" si="9"/>
         <v>2100000</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
@@ -1648,11 +1647,11 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
@@ -1690,11 +1689,11 @@
         <f t="shared" si="9"/>
         <v>653373</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -1732,22 +1731,22 @@
         <f t="shared" si="9"/>
         <v>1680000</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" s="3">
         <v>2000000</v>
@@ -1774,11 +1773,11 @@
         <f t="shared" si="9"/>
         <v>1680000</v>
       </c>
-      <c r="K23" s="10" t="s">
+      <c r="K23" s="8" t="s">
         <v>113</v>
       </c>
       <c r="L23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
@@ -1816,36 +1815,36 @@
         <v>10</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D2" s="8">
         <v>45680</v>
@@ -1863,18 +1862,18 @@
         <v>36</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="D3" s="8">
         <v>45706</v>
@@ -1892,18 +1891,18 @@
         <v>36</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
         <v>52</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D4" s="8">
         <v>45810</v>
@@ -1921,18 +1920,18 @@
         <v>36</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="D5" s="8">
         <v>45832</v>
@@ -1950,18 +1949,18 @@
         <v>48</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="D6" s="8">
         <v>45798</v>
@@ -1979,18 +1978,18 @@
         <v>48</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="8">
         <v>45840</v>
@@ -2008,18 +2007,18 @@
         <v>48</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
         <v>56</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D8" s="8">
         <v>45749</v>
@@ -2037,18 +2036,18 @@
         <v>48</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="D9" s="8">
         <v>45685</v>
@@ -2066,19 +2065,19 @@
         <v>48</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="D10" s="8">
         <v>45838</v>
@@ -2096,19 +2095,19 @@
         <v>48</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D11" s="8">
         <v>45831</v>
@@ -2126,19 +2125,19 @@
         <v>48</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D12" s="8">
         <v>45889</v>
@@ -2156,18 +2155,18 @@
         <v>36</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D13" s="8">
         <v>45889</v>
@@ -2185,18 +2184,18 @@
         <v>24</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D14" s="8">
         <v>45855</v>
@@ -2214,18 +2213,18 @@
         <v>48</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="B15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="D15" s="8">
         <v>45882</v>
@@ -2243,18 +2242,18 @@
         <v>48</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="D16" s="8">
         <v>45870</v>
@@ -2272,18 +2271,18 @@
         <v>48</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="D17" s="8">
         <v>45849</v>
@@ -2301,18 +2300,18 @@
         <v>48</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="D18" s="8">
         <v>45888</v>
@@ -2330,18 +2329,18 @@
         <v>48</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="D19" s="8">
         <v>45877</v>
@@ -2359,18 +2358,18 @@
         <v>48</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="8">
         <v>45911</v>
@@ -2388,18 +2387,18 @@
         <v>48</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="D21" s="8">
         <v>45917</v>
@@ -2417,18 +2416,18 @@
         <v>48</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D22" s="8">
         <v>45958</v>
@@ -2446,18 +2445,18 @@
         <v>48</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D23" s="8">
         <v>45922</v>
@@ -2475,18 +2474,18 @@
         <v>48</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D24" s="8">
         <v>45924</v>
@@ -2504,18 +2503,18 @@
         <v>48</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D25" s="8">
         <v>45988</v>
@@ -2533,18 +2532,18 @@
         <v>48</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" s="8">
         <v>45980</v>
@@ -2562,18 +2561,18 @@
         <v>48</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
         <v>92</v>
       </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" s="8">
         <v>45989</v>
@@ -2591,18 +2590,18 @@
         <v>48</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28" s="8">
         <v>45972</v>
@@ -2620,18 +2619,18 @@
         <v>48</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
         <v>94</v>
       </c>
-      <c r="B29" t="s">
-        <v>95</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="8">
         <v>46022</v>
@@ -2649,18 +2648,18 @@
         <v>48</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D30" s="8">
         <v>46008</v>
@@ -2678,7 +2677,7 @@
         <v>48</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2687,17 +2686,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0e3cc8ea-efda-4ff6-b342-bce7eccffec7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6c8ed8a1-8968-410c-8b4d-03c2f52ac65e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B03A6FCB8D59384FA23E7DEB2EFF06CC" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="01119c67670a03d1687ea3dcab0eae77">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0e3cc8ea-efda-4ff6-b342-bce7eccffec7" xmlns:ns3="6c8ed8a1-8968-410c-8b4d-03c2f52ac65e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9eaad1bb74b921a2f8e6d2096ce39702" ns2:_="" ns3:_="">
     <xsd:import namespace="0e3cc8ea-efda-4ff6-b342-bce7eccffec7"/>
@@ -2886,6 +2874,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0e3cc8ea-efda-4ff6-b342-bce7eccffec7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6c8ed8a1-8968-410c-8b4d-03c2f52ac65e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2896,23 +2895,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4A9654D-50FB-4309-8521-11F07D04ACE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0e3cc8ea-efda-4ff6-b342-bce7eccffec7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6c8ed8a1-8968-410c-8b4d-03c2f52ac65e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97003212-0BFF-4766-A653-CD06BEDDDA0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2931,6 +2913,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4A9654D-50FB-4309-8521-11F07D04ACE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0e3cc8ea-efda-4ff6-b342-bce7eccffec7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6c8ed8a1-8968-410c-8b4d-03c2f52ac65e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ED5781E-F3EE-425C-98FC-F42503DB5E35}">
   <ds:schemaRefs>
